--- a/test/xxx.xlsx
+++ b/test/xxx.xlsx
@@ -317,7 +317,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="string" errorStyle="stop" errorTitle="string" showErrorMessage="true" sqref="A:A" type="list">
+    <dataValidation allowBlank="true" error="请选择模版中的自带指定选项" errorStyle="stop" errorTitle="错误" showErrorMessage="true" sqref="A:A" type="list">
       <formula1>Sheet2!A:A</formula1>
     </dataValidation>
   </dataValidations>
